--- a/imperium-api/generated/quotations/full_quote_test/SNC-FULL-QT-2026-001-R2.xlsx
+++ b/imperium-api/generated/quotations/full_quote_test/SNC-FULL-QT-2026-001-R2.xlsx
@@ -130,7 +130,7 @@
     <t>Audit Trail Hash (Pricing Integrity Key):</t>
   </si>
   <si>
-    <t>c7390a55c78067423181955b38d6587bc7c13bfe49db839ec2642338b002154e</t>
+    <t>83fb7048306a0de2f889ae89a9f52b8f397fa6f81ce751f0a088fb4b75a7e235</t>
   </si>
 </sst>
 </file>

--- a/imperium-api/generated/quotations/full_quote_test/SNC-FULL-QT-2026-001-R2.xlsx
+++ b/imperium-api/generated/quotations/full_quote_test/SNC-FULL-QT-2026-001-R2.xlsx
@@ -130,7 +130,7 @@
     <t>Audit Trail Hash (Pricing Integrity Key):</t>
   </si>
   <si>
-    <t>83fb7048306a0de2f889ae89a9f52b8f397fa6f81ce751f0a088fb4b75a7e235</t>
+    <t>e75b99239ebf5317b23882c64f8ed16865772bd304b04960f707a6279bb66b7f</t>
   </si>
 </sst>
 </file>
